--- a/CPRD Raw Analysis/Results/Output_visits_per_specialty_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_per_specialty_Raw.xlsx
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>560021</v>
+        <v>343369</v>
       </c>
       <c r="C2">
-        <v>82.4061</v>
+        <v>82.6857</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>61529</v>
+        <v>35745</v>
       </c>
       <c r="C3">
-        <v>9.053900000000001</v>
+        <v>8.607699999999999</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>58037</v>
+        <v>36156</v>
       </c>
       <c r="C4">
-        <v>8.539999999999999</v>
+        <v>8.7066</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_per_specialty_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_per_specialty_Raw.xlsx
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>343369</v>
+        <v>290262</v>
       </c>
       <c r="C2">
-        <v>82.6857</v>
+        <v>82.6927</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>35745</v>
+        <v>28608</v>
       </c>
       <c r="C3">
-        <v>8.607699999999999</v>
+        <v>8.1501</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>36156</v>
+        <v>32143</v>
       </c>
       <c r="C4">
-        <v>8.7066</v>
+        <v>9.1572</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_per_specialty_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_per_specialty_Raw.xlsx
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>290262</v>
+        <v>404780</v>
       </c>
       <c r="C2">
-        <v>82.6927</v>
+        <v>82.87050000000001</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>28608</v>
+        <v>40711</v>
       </c>
       <c r="C3">
-        <v>8.1501</v>
+        <v>8.3347</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>32143</v>
+        <v>42958</v>
       </c>
       <c r="C4">
-        <v>9.1572</v>
+        <v>8.7948</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_per_specialty_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_per_specialty_Raw.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -374,40 +374,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Administrative Non-clinical</t>
         </is>
       </c>
       <c r="B2">
-        <v>404780</v>
+        <v>410401</v>
       </c>
       <c r="C2">
-        <v>82.87050000000001</v>
+        <v>37.9794</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B3">
-        <v>40711</v>
+        <v>473745</v>
       </c>
       <c r="C3">
-        <v>8.3347</v>
+        <v>43.8414</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Nurse</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>101524</v>
+      </c>
+      <c r="C4">
+        <v>9.395300000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B4">
-        <v>42958</v>
-      </c>
-      <c r="C4">
-        <v>8.7948</v>
+      <c r="B5">
+        <v>94918</v>
+      </c>
+      <c r="C5">
+        <v>8.783899999999999</v>
       </c>
     </row>
   </sheetData>
